--- a/CITCEA/Calculadora simple/Calculadora simple/CSV/Results/Sizing.xlsx
+++ b/CITCEA/Calculadora simple/Calculadora simple/CSV/Results/Sizing.xlsx
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>484.46</v>
+        <v>565.66</v>
       </c>
     </row>
   </sheetData>
@@ -507,16 +507,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1343</v>
+        <v>1197</v>
       </c>
       <c r="D2" t="n">
-        <v>1343</v>
+        <v>1197</v>
       </c>
       <c r="E2" t="n">
-        <v>1343</v>
+        <v>1197</v>
       </c>
       <c r="F2" t="n">
-        <v>1343</v>
+        <v>1197</v>
       </c>
     </row>
   </sheetData>
@@ -607,10 +607,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>550.28</v>
+        <v>566.96</v>
       </c>
       <c r="D2" t="n">
-        <v>787.62</v>
+        <v>783.63</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>

--- a/CITCEA/Calculadora simple/Calculadora simple/CSV/Results/Sizing.xlsx
+++ b/CITCEA/Calculadora simple/Calculadora simple/CSV/Results/Sizing.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="PV" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Battery" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="other" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="P_hired" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PV" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Battery" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="other" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P_hired" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>565.66</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -507,16 +507,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1197</v>
+        <v>-0</v>
       </c>
       <c r="D2" t="n">
-        <v>1197</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1197</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1197</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -607,10 +607,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>566.96</v>
+        <v>717.71</v>
       </c>
       <c r="D2" t="n">
-        <v>783.63</v>
+        <v>714.95</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
